--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-audit-event-rest.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-audit-event-rest.xlsx
@@ -16166,7 +16166,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
         <v>543</v>
       </c>
@@ -16179,13 +16179,13 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>80</v>
